--- a/ModExample/Defs/excel_data/6任务.xlsx
+++ b/ModExample/Defs/excel_data/6任务.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Territory\数值表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3979BE68-2A64-469D-AF49-9C30D4C4248C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1861C2-ABE2-4D83-8E80-87AC2C4600FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1087,13 +1087,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>封印依靠一份古老的契约维持。
-王城会定期从各地征集居民，
-作为维持封印的代价。
-这一次，轮到你的领地。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>混乱正在蔓延，
 但世界还没有彻底失控。
 在旧秩序崩塌之前，
@@ -1889,12 +1882,20 @@
     <t>start_by_player#bool</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>封印依靠一份古老的契约维持。
+王城会定期从各地征集居民，
+作为维持封印的代价。
+这一次，轮到你的领地。
+你需准备一批杂工，用于献祭。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2433,7 +2434,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AN123"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="9.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.625" customWidth="1"/>
@@ -2467,7 +2468,7 @@
     <col min="40" max="40" width="57" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:40" s="6" customFormat="1" ht="31.5" customHeight="1">
+    <row r="1" spans="1:40" s="6" customFormat="1" ht="31.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>35</v>
       </c>
@@ -2475,7 +2476,7 @@
         <v>36</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>33</v>
@@ -2484,7 +2485,7 @@
         <v>90</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>141</v>
@@ -2493,7 +2494,7 @@
         <v>8</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>79</v>
@@ -2502,10 +2503,10 @@
         <v>243</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>24</v>
@@ -2540,7 +2541,7 @@
         <v>233</v>
       </c>
       <c r="Z1" s="2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="AA1" s="2"/>
       <c r="AB1" s="2" t="s">
@@ -2560,13 +2561,13 @@
       </c>
       <c r="AG1" s="2"/>
       <c r="AH1" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="AI1" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="AJ1" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="AI1" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="AJ1" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="AK1" s="2" t="s">
         <v>5</v>
@@ -2581,7 +2582,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:40" ht="15" customHeight="1">
+    <row r="2" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="10" t="s">
         <v>4</v>
       </c>
@@ -2589,7 +2590,7 @@
         <v>3</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>34</v>
@@ -2598,7 +2599,7 @@
         <v>91</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G2" s="8" t="s">
         <v>142</v>
@@ -2607,7 +2608,7 @@
         <v>27</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J2" s="8" t="s">
         <v>80</v>
@@ -2616,10 +2617,10 @@
         <v>242</v>
       </c>
       <c r="L2" s="8" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="M2" s="8" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="N2" s="8" t="s">
         <v>25</v>
@@ -2652,13 +2653,13 @@
         <v>190</v>
       </c>
       <c r="X2" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Y2" s="8" t="s">
         <v>234</v>
       </c>
       <c r="Z2" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AA2" s="8" t="s">
         <v>0</v>
@@ -2679,16 +2680,16 @@
         <v>149</v>
       </c>
       <c r="AG2" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="AH2" s="11" t="s">
         <v>144</v>
       </c>
       <c r="AI2" s="8" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AJ2" s="11" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AK2" s="8" t="s">
         <v>0</v>
@@ -2704,7 +2705,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:40" ht="15" customHeight="1">
+    <row r="3" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="8">
         <v>1001</v>
       </c>
@@ -2783,7 +2784,7 @@
       </c>
       <c r="AN3" s="14"/>
     </row>
-    <row r="4" spans="1:40" ht="15" customHeight="1">
+    <row r="4" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="8">
         <v>1101</v>
       </c>
@@ -2868,7 +2869,7 @@
       </c>
       <c r="AN4" s="14"/>
     </row>
-    <row r="5" spans="1:40" ht="15" customHeight="1">
+    <row r="5" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="8">
         <v>1201</v>
       </c>
@@ -2955,7 +2956,7 @@
       </c>
       <c r="AN5" s="14"/>
     </row>
-    <row r="6" spans="1:40" ht="15" customHeight="1">
+    <row r="6" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="8">
         <v>1301</v>
       </c>
@@ -3040,7 +3041,7 @@
       </c>
       <c r="AN6" s="14"/>
     </row>
-    <row r="7" spans="1:40" ht="15" customHeight="1">
+    <row r="7" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8">
         <v>1401</v>
       </c>
@@ -3125,7 +3126,7 @@
       </c>
       <c r="AN7" s="14"/>
     </row>
-    <row r="8" spans="1:40" ht="15" customHeight="1">
+    <row r="8" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="8">
         <v>2001</v>
       </c>
@@ -3208,7 +3209,7 @@
       </c>
       <c r="AN8" s="14"/>
     </row>
-    <row r="9" spans="1:40" ht="15" customHeight="1">
+    <row r="9" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="8">
         <v>2101</v>
       </c>
@@ -3295,7 +3296,7 @@
       </c>
       <c r="AN9" s="14"/>
     </row>
-    <row r="10" spans="1:40" ht="15" customHeight="1">
+    <row r="10" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="8">
         <v>2201</v>
       </c>
@@ -3384,7 +3385,7 @@
       </c>
       <c r="AN10" s="14"/>
     </row>
-    <row r="11" spans="1:40" ht="15" customHeight="1">
+    <row r="11" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="8">
         <v>2301</v>
       </c>
@@ -3460,7 +3461,7 @@
       </c>
       <c r="AG11" s="8"/>
       <c r="AH11" s="11" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AI11" s="8"/>
       <c r="AJ11" s="11"/>
@@ -3473,7 +3474,7 @@
       </c>
       <c r="AN11" s="14"/>
     </row>
-    <row r="12" spans="1:40" ht="15" customHeight="1">
+    <row r="12" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="8">
         <v>2401</v>
       </c>
@@ -3547,7 +3548,7 @@
       <c r="AF12" s="8"/>
       <c r="AG12" s="8"/>
       <c r="AH12" s="11" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AI12" s="8"/>
       <c r="AJ12" s="11"/>
@@ -3560,7 +3561,7 @@
       </c>
       <c r="AN12" s="14"/>
     </row>
-    <row r="13" spans="1:40" ht="15" customHeight="1">
+    <row r="13" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="8">
         <v>2501</v>
       </c>
@@ -3645,7 +3646,7 @@
       </c>
       <c r="AN13" s="14"/>
     </row>
-    <row r="14" spans="1:40" ht="15" customHeight="1">
+    <row r="14" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="8">
         <v>2601</v>
       </c>
@@ -3732,7 +3733,7 @@
       </c>
       <c r="AN14" s="14"/>
     </row>
-    <row r="15" spans="1:40" ht="15" customHeight="1">
+    <row r="15" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="8">
         <v>3001</v>
       </c>
@@ -3804,14 +3805,14 @@
       <c r="AJ15" s="11"/>
       <c r="AK15" s="8"/>
       <c r="AL15" s="12" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AM15" s="14" t="s">
         <v>212</v>
       </c>
       <c r="AN15" s="14"/>
     </row>
-    <row r="16" spans="1:40" ht="15" customHeight="1">
+    <row r="16" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8">
         <v>3101</v>
       </c>
@@ -3896,7 +3897,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:40" ht="15" customHeight="1">
+    <row r="17" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="8">
         <v>3201</v>
       </c>
@@ -3981,7 +3982,7 @@
       </c>
       <c r="AN17" s="14"/>
     </row>
-    <row r="18" spans="1:40" ht="15" customHeight="1">
+    <row r="18" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="8">
         <v>3301</v>
       </c>
@@ -4066,7 +4067,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="19" spans="1:40" ht="15" customHeight="1">
+    <row r="19" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8">
         <v>3401</v>
       </c>
@@ -4153,7 +4154,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:40" ht="15" customHeight="1">
+    <row r="20" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="10">
         <v>4001</v>
       </c>
@@ -4228,11 +4229,11 @@
         <v>166</v>
       </c>
       <c r="AM20" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="AN20" s="14"/>
     </row>
-    <row r="21" spans="1:40" ht="15" customHeight="1">
+    <row r="21" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="10">
         <v>4101</v>
       </c>
@@ -4315,7 +4316,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="22" spans="1:40" ht="15" customHeight="1">
+    <row r="22" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="10">
         <v>4201</v>
       </c>
@@ -4398,7 +4399,7 @@
       </c>
       <c r="AN22" s="14"/>
     </row>
-    <row r="23" spans="1:40" ht="15" customHeight="1">
+    <row r="23" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="10">
         <v>4301</v>
       </c>
@@ -4456,7 +4457,7 @@
         <v>226</v>
       </c>
       <c r="X23" s="8" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="Y23" s="8"/>
       <c r="Z23" s="8">
@@ -4485,7 +4486,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="24" spans="1:40" ht="15" customHeight="1">
+    <row r="24" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="10">
         <v>4401</v>
       </c>
@@ -4568,7 +4569,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="25" spans="1:40" ht="15" customHeight="1">
+    <row r="25" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="10">
         <v>5001</v>
       </c>
@@ -4640,14 +4641,14 @@
       <c r="AJ25" s="11"/>
       <c r="AK25" s="8"/>
       <c r="AL25" s="12" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="AM25" s="14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AN25" s="14"/>
     </row>
-    <row r="26" spans="1:40" ht="15" customHeight="1">
+    <row r="26" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="10">
         <v>5101</v>
       </c>
@@ -4702,10 +4703,10 @@
         <v>0</v>
       </c>
       <c r="W26" s="8" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="X26" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="Y26" s="8"/>
       <c r="Z26" s="8">
@@ -4717,7 +4718,7 @@
       <c r="AD26" s="8"/>
       <c r="AE26" s="8"/>
       <c r="AF26" s="8" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="AG26" s="8"/>
       <c r="AH26" s="11"/>
@@ -4726,17 +4727,17 @@
         <v>101</v>
       </c>
       <c r="AK26" s="10" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AL26" s="12" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="AM26" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="AN26" s="14"/>
     </row>
-    <row r="27" spans="1:40" ht="15" customHeight="1">
+    <row r="27" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="10">
         <v>5201</v>
       </c>
@@ -4813,17 +4814,17 @@
         <v>102</v>
       </c>
       <c r="AK27" s="8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AL27" s="12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="AM27" s="14" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AN27" s="14"/>
     </row>
-    <row r="28" spans="1:40" ht="15" customHeight="1">
+    <row r="28" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="10">
         <v>5301</v>
       </c>
@@ -4878,10 +4879,10 @@
         <v>0</v>
       </c>
       <c r="W28" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="X28" s="8" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="Y28" s="8"/>
       <c r="Z28" s="8">
@@ -4893,26 +4894,26 @@
       <c r="AD28" s="8"/>
       <c r="AE28" s="8"/>
       <c r="AF28" s="8" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG28" s="8"/>
       <c r="AH28" s="11"/>
       <c r="AI28" s="8"/>
       <c r="AJ28" s="18" t="s">
+        <v>303</v>
+      </c>
+      <c r="AK28" s="8" t="s">
         <v>304</v>
       </c>
-      <c r="AK28" s="8" t="s">
-        <v>305</v>
-      </c>
       <c r="AL28" s="12" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AM28" s="14" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="AN28" s="14"/>
     </row>
-    <row r="29" spans="1:40" ht="15" customHeight="1">
+    <row r="29" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="10">
         <v>5401</v>
       </c>
@@ -4980,7 +4981,7 @@
       <c r="AD29" s="8"/>
       <c r="AE29" s="8"/>
       <c r="AF29" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="AG29" s="8"/>
       <c r="AH29" s="11"/>
@@ -4988,14 +4989,14 @@
       <c r="AJ29" s="11"/>
       <c r="AK29" s="8"/>
       <c r="AL29" s="12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AM29" s="14" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AN29" s="14"/>
     </row>
-    <row r="30" spans="1:40" ht="15" customHeight="1">
+    <row r="30" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="10">
         <v>6001</v>
       </c>
@@ -5067,14 +5068,14 @@
       <c r="AJ30" s="11"/>
       <c r="AK30" s="8"/>
       <c r="AL30" s="12" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AM30" s="14" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AN30" s="14"/>
     </row>
-    <row r="31" spans="1:40" ht="15" customHeight="1">
+    <row r="31" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="10">
         <v>6101</v>
       </c>
@@ -5129,10 +5130,10 @@
         <v>0</v>
       </c>
       <c r="W31" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="X31" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="X31" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="Y31" s="8"/>
       <c r="Z31" s="8">
@@ -5144,7 +5145,7 @@
       <c r="AD31" s="8"/>
       <c r="AE31" s="8"/>
       <c r="AF31" s="8" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="AG31" s="8"/>
       <c r="AH31" s="11"/>
@@ -5156,14 +5157,14 @@
         <v>67</v>
       </c>
       <c r="AL31" s="12" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AM31" s="27" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AN31" s="14"/>
     </row>
-    <row r="32" spans="1:40" ht="15" customHeight="1">
+    <row r="32" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="10">
         <v>6201</v>
       </c>
@@ -5218,10 +5219,10 @@
         <v>0</v>
       </c>
       <c r="W32" s="2" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="X32" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="Y32" s="8"/>
       <c r="Z32" s="8">
@@ -5233,10 +5234,10 @@
       <c r="AD32" s="8"/>
       <c r="AE32" s="8"/>
       <c r="AF32" s="8" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="AG32" s="11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AH32" s="11"/>
       <c r="AI32" s="8"/>
@@ -5247,14 +5248,14 @@
         <v>68</v>
       </c>
       <c r="AL32" s="12" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AM32" s="27" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AN32" s="14"/>
     </row>
-    <row r="33" spans="1:40" ht="15" customHeight="1">
+    <row r="33" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="10">
         <v>6301</v>
       </c>
@@ -5309,10 +5310,10 @@
         <v>0</v>
       </c>
       <c r="W33" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="X33" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="Y33" s="8"/>
       <c r="Z33" s="8">
@@ -5324,10 +5325,10 @@
       <c r="AD33" s="8"/>
       <c r="AE33" s="8"/>
       <c r="AF33" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="AG33" s="11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="AH33" s="11"/>
       <c r="AI33" s="8"/>
@@ -5338,14 +5339,14 @@
         <v>69</v>
       </c>
       <c r="AL33" s="12" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="AM33" s="27" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="AN33" s="14"/>
     </row>
-    <row r="34" spans="1:40" ht="15" customHeight="1">
+    <row r="34" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="10">
         <v>6401</v>
       </c>
@@ -5400,10 +5401,10 @@
         <v>0</v>
       </c>
       <c r="W34" s="8" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="X34" s="8" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="Y34" s="8"/>
       <c r="Z34" s="8">
@@ -5415,10 +5416,10 @@
       <c r="AD34" s="8"/>
       <c r="AE34" s="8"/>
       <c r="AF34" s="8" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="AG34" s="11" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AH34" s="11"/>
       <c r="AI34" s="8"/>
@@ -5429,14 +5430,14 @@
         <v>70</v>
       </c>
       <c r="AL34" s="12" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AM34" s="27" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AN34" s="14"/>
     </row>
-    <row r="35" spans="1:40" ht="15" customHeight="1">
+    <row r="35" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="10">
         <v>901000</v>
       </c>
@@ -5510,14 +5511,14 @@
       <c r="AJ35" s="11"/>
       <c r="AK35" s="8"/>
       <c r="AL35" s="12" t="s">
+        <v>284</v>
+      </c>
+      <c r="AM35" s="14" t="s">
         <v>285</v>
-      </c>
-      <c r="AM35" s="14" t="s">
-        <v>286</v>
       </c>
       <c r="AN35" s="14"/>
     </row>
-    <row r="36" spans="1:40" ht="15" customHeight="1">
+    <row r="36" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="10">
         <v>901001</v>
       </c>
@@ -5583,10 +5584,10 @@
       <c r="AD36" s="16"/>
       <c r="AE36" s="8"/>
       <c r="AF36" s="8" t="s">
+        <v>327</v>
+      </c>
+      <c r="AG36" s="8" t="s">
         <v>328</v>
-      </c>
-      <c r="AG36" s="8" t="s">
-        <v>329</v>
       </c>
       <c r="AH36" s="11"/>
       <c r="AI36" s="8"/>
@@ -5602,7 +5603,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="37" spans="1:40" ht="15" customHeight="1">
+    <row r="37" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="10">
         <v>902001</v>
       </c>
@@ -5668,10 +5669,10 @@
       <c r="AD37" s="16"/>
       <c r="AE37" s="8"/>
       <c r="AF37" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="AG37" s="8" t="s">
         <v>330</v>
-      </c>
-      <c r="AG37" s="8" t="s">
-        <v>331</v>
       </c>
       <c r="AH37" s="11"/>
       <c r="AI37" s="8"/>
@@ -5687,7 +5688,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="38" spans="1:40" ht="15" customHeight="1">
+    <row r="38" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="10">
         <v>903001</v>
       </c>
@@ -5753,10 +5754,10 @@
       <c r="AD38" s="16"/>
       <c r="AE38" s="8"/>
       <c r="AF38" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="AG38" s="8" t="s">
         <v>326</v>
-      </c>
-      <c r="AG38" s="8" t="s">
-        <v>327</v>
       </c>
       <c r="AH38" s="11"/>
       <c r="AI38" s="8"/>
@@ -5772,7 +5773,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="1:40" ht="15" customHeight="1">
+    <row r="39" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="10">
         <v>904001</v>
       </c>
@@ -5844,10 +5845,10 @@
       <c r="AD39" s="16"/>
       <c r="AE39" s="8"/>
       <c r="AF39" s="8" t="s">
+        <v>325</v>
+      </c>
+      <c r="AG39" s="8" t="s">
         <v>326</v>
-      </c>
-      <c r="AG39" s="8" t="s">
-        <v>327</v>
       </c>
       <c r="AH39" s="11"/>
       <c r="AI39" s="8"/>
@@ -5863,7 +5864,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="40" spans="1:40" ht="15" customHeight="1">
+    <row r="40" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="10">
         <v>101005</v>
       </c>
@@ -5935,14 +5936,14 @@
       <c r="AJ40" s="11"/>
       <c r="AK40" s="8"/>
       <c r="AL40" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AM40" s="14" t="s">
         <v>83</v>
       </c>
       <c r="AN40" s="14"/>
     </row>
-    <row r="41" spans="1:40" ht="15" customHeight="1">
+    <row r="41" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="10">
         <v>10100501</v>
       </c>
@@ -5986,7 +5987,7 @@
       <c r="P41" s="8"/>
       <c r="Q41" s="8"/>
       <c r="R41" s="8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="S41" s="8"/>
       <c r="T41" s="8">
@@ -6029,13 +6030,13 @@
         <v>84</v>
       </c>
       <c r="AM41" s="27" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="AN41" s="14" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
-    <row r="42" spans="1:40" ht="15" customHeight="1">
+    <row r="42" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="10">
         <v>10100502</v>
       </c>
@@ -6079,7 +6080,7 @@
       <c r="P42" s="8"/>
       <c r="Q42" s="8"/>
       <c r="R42" s="8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="S42" s="8"/>
       <c r="T42" s="8">
@@ -6122,13 +6123,13 @@
         <v>85</v>
       </c>
       <c r="AM42" s="27" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AN42" s="14" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
-    <row r="43" spans="1:40" ht="15" customHeight="1">
+    <row r="43" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="10">
         <v>10100503</v>
       </c>
@@ -6172,7 +6173,7 @@
       <c r="P43" s="8"/>
       <c r="Q43" s="8"/>
       <c r="R43" s="8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="S43" s="8"/>
       <c r="T43" s="8">
@@ -6215,13 +6216,13 @@
         <v>86</v>
       </c>
       <c r="AM43" s="27" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AN43" s="14" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
-    <row r="44" spans="1:40" ht="15" customHeight="1">
+    <row r="44" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="10">
         <v>10100504</v>
       </c>
@@ -6265,7 +6266,7 @@
       <c r="P44" s="8"/>
       <c r="Q44" s="8"/>
       <c r="R44" s="8" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="S44" s="8"/>
       <c r="T44" s="8">
@@ -6308,13 +6309,13 @@
         <v>87</v>
       </c>
       <c r="AM44" s="27" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="AN44" s="14" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
-    <row r="45" spans="1:40" ht="15" customHeight="1">
+    <row r="45" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="10">
         <v>909001</v>
       </c>
@@ -6389,13 +6390,13 @@
         <v>105</v>
       </c>
       <c r="AM45" s="14" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AN45" s="26" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="46" spans="1:40" ht="15" customHeight="1">
+    <row r="46" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="10">
         <v>910001</v>
       </c>
@@ -6444,7 +6445,7 @@
         <v>188</v>
       </c>
       <c r="S46" s="9" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="T46" s="8">
         <v>0</v>
@@ -6484,7 +6485,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="1:40" ht="15" customHeight="1">
+    <row r="47" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="10">
         <v>7001</v>
       </c>
@@ -6556,14 +6557,14 @@
       <c r="AJ47" s="11"/>
       <c r="AK47" s="8"/>
       <c r="AL47" s="12" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="AM47" s="27" t="s">
         <v>253</v>
       </c>
       <c r="AN47" s="14"/>
     </row>
-    <row r="48" spans="1:40" ht="15" customHeight="1">
+    <row r="48" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="10">
         <v>7101</v>
       </c>
@@ -6642,7 +6643,7 @@
       </c>
       <c r="AN48" s="14"/>
     </row>
-    <row r="49" spans="1:40" ht="15" customHeight="1">
+    <row r="49" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="10">
         <v>7201</v>
       </c>
@@ -6720,14 +6721,14 @@
       <c r="AL49" s="12" t="s">
         <v>249</v>
       </c>
-      <c r="AM49" s="14" t="s">
-        <v>255</v>
+      <c r="AM49" s="27" t="s">
+        <v>414</v>
       </c>
       <c r="AN49" s="14" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="50" spans="1:40" ht="15" customHeight="1">
+    <row r="50" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="10">
         <v>7301</v>
       </c>
@@ -6797,26 +6798,26 @@
       <c r="AD50" s="8"/>
       <c r="AE50" s="8"/>
       <c r="AF50" s="8" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG50" s="8" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="AH50" s="11"/>
       <c r="AI50" s="8"/>
       <c r="AJ50" s="11"/>
       <c r="AK50" s="8" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AL50" s="12" t="s">
         <v>250</v>
       </c>
       <c r="AM50" s="27" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AN50" s="14"/>
     </row>
-    <row r="51" spans="1:40" ht="15" customHeight="1">
+    <row r="51" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="10">
         <v>7401</v>
       </c>
@@ -6886,26 +6887,26 @@
       <c r="AD51" s="8"/>
       <c r="AE51" s="8"/>
       <c r="AF51" s="8" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="AG51" s="8" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="AH51" s="11"/>
       <c r="AI51" s="8"/>
       <c r="AJ51" s="11"/>
       <c r="AK51" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AL51" s="12" t="s">
         <v>247</v>
       </c>
       <c r="AM51" s="27" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AN51" s="14"/>
     </row>
-    <row r="52" spans="1:40" ht="15" customHeight="1">
+    <row r="52" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="10">
         <v>7501</v>
       </c>
@@ -6975,26 +6976,26 @@
       <c r="AD52" s="8"/>
       <c r="AE52" s="8"/>
       <c r="AF52" s="8" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AG52" s="10" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AH52" s="11"/>
       <c r="AI52" s="8"/>
       <c r="AJ52" s="11"/>
       <c r="AK52" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="AL52" s="12" t="s">
         <v>251</v>
       </c>
       <c r="AM52" s="27" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AN52" s="14"/>
     </row>
-    <row r="53" spans="1:40" ht="15" customHeight="1">
+    <row r="53" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="10">
         <v>7601</v>
       </c>
@@ -7069,17 +7070,17 @@
       <c r="AI53" s="8"/>
       <c r="AJ53" s="11"/>
       <c r="AK53" s="8" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="AL53" s="12" t="s">
         <v>248</v>
       </c>
       <c r="AM53" s="14" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AN53" s="14"/>
     </row>
-    <row r="54" spans="1:40" ht="15" customHeight="1">
+    <row r="54" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="10">
         <v>905000</v>
       </c>
@@ -7151,12 +7152,12 @@
       <c r="AJ54" s="11"/>
       <c r="AK54" s="8"/>
       <c r="AL54" s="12" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AM54" s="14"/>
       <c r="AN54" s="14"/>
     </row>
-    <row r="55" spans="1:40" ht="15" customHeight="1">
+    <row r="55" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="10">
         <v>905001</v>
       </c>
@@ -7243,7 +7244,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="1:40" ht="15" customHeight="1">
+    <row r="56" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="10">
         <v>906001</v>
       </c>
@@ -7316,7 +7317,7 @@
       <c r="AE56" s="8"/>
       <c r="AF56" s="8"/>
       <c r="AG56" s="8" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AH56" s="11"/>
       <c r="AI56" s="8"/>
@@ -7326,13 +7327,13 @@
         <v>126</v>
       </c>
       <c r="AM56" s="14" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AN56" s="14" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="1:40" ht="15" customHeight="1">
+    <row r="57" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="10">
         <v>907001</v>
       </c>
@@ -7413,11 +7414,11 @@
         <v>106</v>
       </c>
       <c r="AM57" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AN57" s="14"/>
     </row>
-    <row r="58" spans="1:40" ht="15" customHeight="1">
+    <row r="58" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="10">
         <v>912001</v>
       </c>
@@ -7494,13 +7495,13 @@
         <v>107</v>
       </c>
       <c r="AM58" s="27" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AN58" s="26" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="59" spans="1:40" ht="15" customHeight="1">
+    <row r="59" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="10">
         <v>913001</v>
       </c>
@@ -7587,7 +7588,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="60" spans="1:40" ht="15" customHeight="1">
+    <row r="60" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="10">
         <v>914001</v>
       </c>
@@ -7674,7 +7675,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="61" spans="1:40" ht="15" customHeight="1">
+    <row r="61" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="10">
         <v>9001</v>
       </c>
@@ -7746,14 +7747,14 @@
       <c r="AJ61" s="11"/>
       <c r="AK61" s="8"/>
       <c r="AL61" s="14" t="s">
+        <v>274</v>
+      </c>
+      <c r="AM61" s="14" t="s">
         <v>275</v>
-      </c>
-      <c r="AM61" s="14" t="s">
-        <v>276</v>
       </c>
       <c r="AN61" s="14"/>
     </row>
-    <row r="62" spans="1:40" ht="27" customHeight="1">
+    <row r="62" spans="1:40" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="10">
         <v>9101</v>
       </c>
@@ -7821,26 +7822,26 @@
       <c r="AD62" s="8"/>
       <c r="AE62" s="8"/>
       <c r="AF62" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="AG62" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AH62" s="11"/>
       <c r="AI62" s="8"/>
       <c r="AJ62" s="11"/>
       <c r="AK62" s="8"/>
       <c r="AL62" s="14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="AM62" s="27" t="s">
+        <v>359</v>
+      </c>
+      <c r="AN62" s="27" t="s">
         <v>360</v>
       </c>
-      <c r="AN62" s="27" t="s">
-        <v>361</v>
-      </c>
     </row>
-    <row r="63" spans="1:40" ht="29.25" customHeight="1">
+    <row r="63" spans="1:40" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="10">
         <v>9201</v>
       </c>
@@ -7897,10 +7898,10 @@
         <v>0</v>
       </c>
       <c r="W63" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="X63" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="X63" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="Y63" s="8"/>
       <c r="Z63" s="8">
@@ -7912,10 +7913,10 @@
       <c r="AD63" s="8"/>
       <c r="AE63" s="8"/>
       <c r="AF63" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="AG63" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="AG63" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="AH63" s="11"/>
       <c r="AI63" s="8"/>
@@ -7924,14 +7925,14 @@
       </c>
       <c r="AK63" s="8"/>
       <c r="AL63" s="14" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AM63" s="27" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AN63" s="14"/>
     </row>
-    <row r="64" spans="1:40" ht="15" customHeight="1">
+    <row r="64" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="10">
         <v>9301</v>
       </c>
@@ -8001,10 +8002,10 @@
       <c r="AD64" s="8"/>
       <c r="AE64" s="8"/>
       <c r="AF64" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="AG64" s="8" t="s">
         <v>372</v>
-      </c>
-      <c r="AG64" s="8" t="s">
-        <v>373</v>
       </c>
       <c r="AH64" s="11"/>
       <c r="AI64" s="8"/>
@@ -8013,14 +8014,14 @@
       </c>
       <c r="AK64" s="8"/>
       <c r="AL64" s="14" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AM64" s="27" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AN64" s="14"/>
     </row>
-    <row r="65" spans="1:40" ht="41.25" customHeight="1">
+    <row r="65" spans="1:40" ht="41.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="10">
         <v>9401</v>
       </c>
@@ -8077,10 +8078,10 @@
         <v>0</v>
       </c>
       <c r="W65" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="X65" s="2" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="Y65" s="8"/>
       <c r="Z65" s="8">
@@ -8092,26 +8093,26 @@
       <c r="AD65" s="8"/>
       <c r="AE65" s="8"/>
       <c r="AF65" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AG65" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="AH65" s="11"/>
       <c r="AI65" s="8"/>
       <c r="AJ65" s="18" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AK65" s="8"/>
       <c r="AL65" s="14" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="AM65" s="27" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="AN65" s="14"/>
     </row>
-    <row r="66" spans="1:40" ht="27" customHeight="1">
+    <row r="66" spans="1:40" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="10">
         <v>10101</v>
       </c>
@@ -8183,14 +8184,14 @@
       <c r="AJ66" s="11"/>
       <c r="AK66" s="8"/>
       <c r="AL66" s="14" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AM66" s="14" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="AN66" s="14"/>
     </row>
-    <row r="67" spans="1:40" ht="15" customHeight="1">
+    <row r="67" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="10">
         <v>10102</v>
       </c>
@@ -8271,13 +8272,13 @@
         <v>9</v>
       </c>
       <c r="AM67" s="14" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AN67" s="14" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="68" spans="1:40" ht="15" customHeight="1">
+    <row r="68" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="10">
         <v>10103</v>
       </c>
@@ -8364,7 +8365,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:40" ht="15" customHeight="1">
+    <row r="69" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="10">
         <v>10104</v>
       </c>
@@ -8442,16 +8443,16 @@
       <c r="AJ69" s="11"/>
       <c r="AK69" s="8"/>
       <c r="AL69" s="12" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AM69" s="27" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AN69" s="14" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
-    <row r="70" spans="1:40" ht="29.25" customHeight="1">
+    <row r="70" spans="1:40" ht="29.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="10">
         <v>10105</v>
       </c>
@@ -8529,14 +8530,14 @@
       <c r="AJ70" s="11"/>
       <c r="AK70" s="8"/>
       <c r="AL70" s="12" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="AM70" s="27" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AN70" s="14"/>
     </row>
-    <row r="71" spans="1:40" ht="15" customHeight="1">
+    <row r="71" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="10">
         <v>10106</v>
       </c>
@@ -8621,7 +8622,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="72" spans="1:40" ht="15" customHeight="1">
+    <row r="72" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="10">
         <v>10107</v>
       </c>
@@ -8706,7 +8707,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="73" spans="1:40" ht="15" customHeight="1">
+    <row r="73" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="10">
         <v>10108</v>
       </c>
@@ -8791,7 +8792,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="74" spans="1:40" ht="15" customHeight="1">
+    <row r="74" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="10">
         <v>10109</v>
       </c>
@@ -8876,7 +8877,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="75" spans="1:40" ht="15" customHeight="1">
+    <row r="75" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="10">
         <v>10110</v>
       </c>
@@ -8961,7 +8962,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="76" spans="1:40" ht="15" customHeight="1">
+    <row r="76" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="10">
         <v>10111</v>
       </c>
@@ -9046,7 +9047,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="77" spans="1:40" ht="57" customHeight="1">
+    <row r="77" spans="1:40" ht="57" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="20">
         <v>102001</v>
       </c>
@@ -9120,14 +9121,14 @@
       <c r="AJ77" s="11"/>
       <c r="AK77" s="8"/>
       <c r="AL77" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AM77" s="27" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="AN77" s="14"/>
     </row>
-    <row r="78" spans="1:40" ht="33" customHeight="1">
+    <row r="78" spans="1:40" ht="33" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="20">
         <v>10200101</v>
       </c>
@@ -9203,16 +9204,16 @@
       <c r="AJ78" s="11"/>
       <c r="AK78" s="8"/>
       <c r="AL78" s="8" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AM78" s="27" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AN78" s="14" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="79" spans="1:40" ht="15" customHeight="1">
+    <row r="79" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="20">
         <v>102002</v>
       </c>
@@ -9291,7 +9292,7 @@
       </c>
       <c r="AN79" s="14"/>
     </row>
-    <row r="80" spans="1:40" ht="15" customHeight="1">
+    <row r="80" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="20">
         <v>10200201</v>
       </c>
@@ -9376,7 +9377,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="81" spans="1:40" ht="15" customHeight="1">
+    <row r="81" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="20">
         <v>10200202</v>
       </c>
@@ -9461,7 +9462,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="82" spans="1:40" ht="15" customHeight="1">
+    <row r="82" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="20">
         <v>10200203</v>
       </c>
@@ -9546,7 +9547,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="83" spans="1:40" ht="15" customHeight="1">
+    <row r="83" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="20">
         <v>10200204</v>
       </c>
@@ -9631,7 +9632,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="1:40" ht="15" customHeight="1">
+    <row r="84" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="20">
         <v>10200205</v>
       </c>
@@ -9716,7 +9717,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="85" spans="1:40" ht="15" customHeight="1">
+    <row r="85" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="20">
         <v>10200206</v>
       </c>
@@ -9801,7 +9802,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="86" spans="1:40" ht="42" customHeight="1">
+    <row r="86" spans="1:40" ht="42" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="20">
         <v>10201</v>
       </c>
@@ -9856,10 +9857,10 @@
         <v>0</v>
       </c>
       <c r="W86" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="X86" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Y86" s="8"/>
       <c r="Z86" s="8">
@@ -9874,19 +9875,19 @@
       <c r="AG86" s="8"/>
       <c r="AH86" s="11"/>
       <c r="AI86" s="14" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AJ86" s="11"/>
       <c r="AK86" s="8"/>
       <c r="AL86" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AM86" s="27" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="AN86" s="14"/>
     </row>
-    <row r="87" spans="1:40" ht="15" customHeight="1">
+    <row r="87" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="20">
         <v>10202</v>
       </c>
@@ -9958,14 +9959,14 @@
       <c r="AJ87" s="11"/>
       <c r="AK87" s="8"/>
       <c r="AL87" s="8" t="s">
+        <v>379</v>
+      </c>
+      <c r="AM87" s="14" t="s">
         <v>380</v>
-      </c>
-      <c r="AM87" s="14" t="s">
-        <v>381</v>
       </c>
       <c r="AN87" s="14"/>
     </row>
-    <row r="88" spans="1:40" ht="15" customHeight="1">
+    <row r="88" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="20">
         <v>10203</v>
       </c>
@@ -10046,7 +10047,7 @@
       </c>
       <c r="AN88" s="14"/>
     </row>
-    <row r="89" spans="1:40" ht="15" customHeight="1">
+    <row r="89" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="20">
         <v>10204</v>
       </c>
@@ -10127,7 +10128,7 @@
       </c>
       <c r="AN89" s="14"/>
     </row>
-    <row r="90" spans="1:40" ht="15" customHeight="1">
+    <row r="90" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="20">
         <v>10205</v>
       </c>
@@ -10193,14 +10194,14 @@
       <c r="AJ90" s="11"/>
       <c r="AK90" s="8"/>
       <c r="AL90" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="AM90" s="14" t="s">
         <v>382</v>
-      </c>
-      <c r="AM90" s="14" t="s">
-        <v>383</v>
       </c>
       <c r="AN90" s="14"/>
     </row>
-    <row r="91" spans="1:40" ht="17.25" customHeight="1">
+    <row r="91" spans="1:40" ht="17.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="20">
         <v>103001</v>
       </c>
@@ -10277,11 +10278,11 @@
         <v>62</v>
       </c>
       <c r="AM91" s="27" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="AN91" s="14"/>
     </row>
-    <row r="92" spans="1:40" ht="15" customHeight="1">
+    <row r="92" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="20">
         <v>101115</v>
       </c>
@@ -10362,7 +10363,7 @@
       </c>
       <c r="AN92" s="14"/>
     </row>
-    <row r="93" spans="1:40" ht="15" customHeight="1">
+    <row r="93" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="20">
         <v>10111501</v>
       </c>
@@ -10447,7 +10448,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="94" spans="1:40" ht="15" customHeight="1">
+    <row r="94" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="20">
         <v>10111502</v>
       </c>
@@ -10532,7 +10533,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="95" spans="1:40" ht="15" customHeight="1">
+    <row r="95" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="20">
         <v>10111503</v>
       </c>
@@ -10617,7 +10618,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="96" spans="1:40" ht="15" customHeight="1">
+    <row r="96" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="20">
         <v>10111504</v>
       </c>
@@ -10702,7 +10703,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="97" spans="1:40" ht="15" customHeight="1">
+    <row r="97" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="20">
         <v>10111505</v>
       </c>
@@ -10787,7 +10788,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="98" spans="1:40" ht="15" customHeight="1">
+    <row r="98" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="20">
         <v>10111506</v>
       </c>
@@ -10872,7 +10873,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="99" spans="1:40" ht="15" customHeight="1">
+    <row r="99" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="20">
         <v>10111507</v>
       </c>
@@ -10957,7 +10958,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="100" spans="1:40" ht="15" customHeight="1">
+    <row r="100" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="20">
         <v>101116</v>
       </c>
@@ -11012,10 +11013,10 @@
         <v>0</v>
       </c>
       <c r="W100" s="2" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="X100" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="Y100" s="8"/>
       <c r="Z100" s="8">
@@ -11030,7 +11031,7 @@
       <c r="AG100" s="8"/>
       <c r="AH100" s="11"/>
       <c r="AI100" s="14" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="AJ100" s="11"/>
       <c r="AK100" s="8"/>
@@ -11038,13 +11039,13 @@
         <v>73</v>
       </c>
       <c r="AM100" s="27" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AN100" s="28" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="101" spans="1:40" ht="15" customHeight="1">
+    <row r="101" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="20">
         <v>101117</v>
       </c>
@@ -11127,7 +11128,7 @@
       </c>
       <c r="AN101" s="14"/>
     </row>
-    <row r="102" spans="1:40" ht="15" customHeight="1">
+    <row r="102" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="20">
         <v>101118</v>
       </c>
@@ -11210,7 +11211,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="103" spans="1:40" ht="15" customHeight="1">
+    <row r="103" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="20">
         <v>101119</v>
       </c>
@@ -11295,7 +11296,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="104" spans="1:40" ht="15" customHeight="1">
+    <row r="104" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="20">
         <v>101120</v>
       </c>
@@ -11380,7 +11381,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="105" spans="1:40" ht="15" customHeight="1">
+    <row r="105" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="20">
         <v>101121</v>
       </c>
@@ -11465,7 +11466,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="106" spans="1:40" ht="15" customHeight="1">
+    <row r="106" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="20">
         <v>101122</v>
       </c>
@@ -11550,7 +11551,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="107" spans="1:40" ht="15" customHeight="1">
+    <row r="107" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="20">
         <v>1011220</v>
       </c>
@@ -11635,7 +11636,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="108" spans="1:40" ht="15" customHeight="1">
+    <row r="108" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="20">
         <v>1011230</v>
       </c>
@@ -11707,14 +11708,14 @@
       <c r="AJ108" s="11"/>
       <c r="AK108" s="8"/>
       <c r="AL108" s="8" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AM108" s="14" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AN108" s="14"/>
     </row>
-    <row r="109" spans="1:40" ht="15" customHeight="1">
+    <row r="109" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="20">
         <v>101123</v>
       </c>
@@ -11793,7 +11794,7 @@
       </c>
       <c r="AN109" s="14"/>
     </row>
-    <row r="110" spans="1:40" ht="15" customHeight="1">
+    <row r="110" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="20">
         <v>101124</v>
       </c>
@@ -11872,7 +11873,7 @@
       </c>
       <c r="AN110" s="14"/>
     </row>
-    <row r="111" spans="1:40" ht="15" customHeight="1">
+    <row r="111" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="20">
         <v>1011240</v>
       </c>
@@ -11936,14 +11937,14 @@
       <c r="AJ111" s="11"/>
       <c r="AK111" s="8"/>
       <c r="AL111" s="8" t="s">
+        <v>381</v>
+      </c>
+      <c r="AM111" s="14" t="s">
         <v>382</v>
-      </c>
-      <c r="AM111" s="14" t="s">
-        <v>383</v>
       </c>
       <c r="AN111" s="14"/>
     </row>
-    <row r="112" spans="1:40" ht="51.75" customHeight="1">
+    <row r="112" spans="1:40" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="20">
         <v>101125</v>
       </c>
@@ -12013,10 +12014,10 @@
       <c r="AD112" s="8"/>
       <c r="AE112" s="8"/>
       <c r="AF112" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="AG112" s="2" t="s">
         <v>401</v>
-      </c>
-      <c r="AG112" s="2" t="s">
-        <v>402</v>
       </c>
       <c r="AH112" s="11"/>
       <c r="AI112" s="8"/>
@@ -12026,13 +12027,13 @@
         <v>76</v>
       </c>
       <c r="AM112" s="27" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AN112" s="27" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="113" spans="1:40" ht="15" customHeight="1">
+    <row r="113" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="20">
         <v>101126</v>
       </c>
@@ -12109,11 +12110,11 @@
         <v>62</v>
       </c>
       <c r="AM113" s="27" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AN113" s="14"/>
     </row>
-    <row r="123" spans="1:40" ht="15" customHeight="1">
+    <row r="123" spans="1:40" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="AK123" s="7"/>
     </row>
   </sheetData>
